--- a/prisma/guest.xlsx
+++ b/prisma/guest.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karla\Documents\GitHub\wedding_backend\prisma\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E36AF1-80C3-4469-A038-A2970FF893E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1 - Table 4-1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet 1 - Table 4-1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="211">
-  <si>
-    <t>Table 4-1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
   <si>
     <t>Martin Pocasangre</t>
   </si>
@@ -644,23 +650,21 @@
   </si>
   <si>
     <t>Alberto Pacas C</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Grupo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
     </font>
@@ -670,12 +674,7 @@
       <name val="Proxima Nova"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Proxima Nova"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Proxima Nova"/>
@@ -772,60 +771,57 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -836,26 +832,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff7f7f7f"/>
-      <rgbColor rgb="ffa6c06a"/>
-      <rgbColor rgb="ffffd0e7"/>
-      <rgbColor rgb="fff0b76e"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FFA6C06A"/>
+      <rgbColor rgb="FFFFD0E7"/>
+      <rgbColor rgb="FFF0B76E"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Blank">
   <a:themeElements>
     <a:clrScheme name="Blank">
       <a:dk1>
@@ -1054,7 +1109,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1072,7 +1127,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1200" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1101,7 +1156,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1126,7 +1181,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1151,7 +1206,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1176,7 +1231,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1201,7 +1256,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1226,7 +1281,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1251,7 +1306,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1276,7 +1331,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1301,7 +1356,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1314,9 +1369,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1333,7 +1394,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1351,7 +1412,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1376,7 +1437,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1401,7 +1462,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1426,7 +1487,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1451,7 +1512,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1476,7 +1537,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1501,7 +1562,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1526,7 +1587,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1551,7 +1612,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1576,7 +1637,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1589,9 +1650,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1605,7 +1672,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="50800" tIns="50800" rIns="50800" bIns="50800" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1623,7 +1690,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1652,7 +1719,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1677,7 +1744,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1702,7 +1769,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1727,7 +1794,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1752,7 +1819,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1777,7 +1844,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1802,7 +1869,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1827,7 +1894,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1852,7 +1919,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1865,1725 +1932,1728 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:B213"/>
-  <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="18" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B212"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="22.6562" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="2" width="22.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="16.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:2" ht="20.7" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="22.8" customHeight="1">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" ht="20.75" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-    </row>
-    <row r="3" ht="22.75" customHeight="1">
-      <c r="A3" t="s" s="4">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+    </row>
+    <row r="3" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" t="s" s="6">
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" t="s" s="6">
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" t="s" s="6">
+    <row r="6" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" t="s" s="6">
+    <row r="7" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" t="s" s="6">
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" t="s" s="6">
+    <row r="9" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" t="s" s="6">
+      <c r="B9" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" t="s" s="6">
+    <row r="11" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" t="s" s="6">
+      <c r="B11" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" t="s" s="6">
+    <row r="13" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" t="s" s="6">
+      <c r="B13" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" t="s" s="6">
+    <row r="15" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" t="s" s="8">
+    <row r="16" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" t="s" s="6">
+      <c r="B16" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" t="s" s="6">
+      <c r="B17" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" t="s" s="6">
+      <c r="B18" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>9</v>
       </c>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" t="s" s="6">
+    <row r="20" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" t="s" s="6">
+      <c r="B20" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" t="s" s="6">
+    <row r="22" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A22" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" t="s" s="10">
+      <c r="B22" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" t="s" s="6">
+    <row r="24" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" t="s" s="10">
+      <c r="B24" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A25" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>12</v>
       </c>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" t="s" s="10">
+    <row r="26" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" t="s" s="6">
+      <c r="B26" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" t="s" s="6">
+    <row r="28" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A28" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" t="s" s="10">
+      <c r="B28" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" t="s" s="6">
+    <row r="30" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" t="s" s="6">
+      <c r="B30" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A31" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" t="s" s="6">
+      <c r="B31" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" t="s" s="6">
+    <row r="33" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" t="s" s="6">
+    <row r="34" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A34" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" t="s" s="6">
+    <row r="35" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" t="s" s="8">
+      <c r="B35" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="6">
         <v>17</v>
       </c>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" t="s" s="6">
+    <row r="37" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A37" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="7">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" t="s" s="8">
+      <c r="B37" s="8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" t="s" s="6">
+    <row r="39" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" t="s" s="6">
+      <c r="B39" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" t="s" s="6">
+      <c r="B40" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A41" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="12">
         <v>20</v>
       </c>
     </row>
-    <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" t="s" s="12">
+    <row r="42" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A42" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" t="s" s="12">
+      <c r="B42" s="12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A43" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="13">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" t="s" s="12">
+      <c r="B43" s="12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A44" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="13">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" t="s" s="12">
+      <c r="B44" s="12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="6">
         <v>23</v>
       </c>
     </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" t="s" s="6">
+    <row r="46" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A46" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="7">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" t="s" s="12">
+      <c r="B46" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A47" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="13">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" t="s" s="12">
+      <c r="B47" s="12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A48" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" t="s" s="6">
+    <row r="49" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A49" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="7">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" t="s" s="10">
+      <c r="B49" s="10">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A50" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="11">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" t="s" s="10">
+      <c r="B50" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A51" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="6">
         <v>27</v>
       </c>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" t="s" s="6">
+    <row r="52" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A52" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="7">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" t="s" s="10">
+      <c r="B52" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A53" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="6">
         <v>28</v>
       </c>
     </row>
-    <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" t="s" s="6">
+    <row r="54" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A54" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="7">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" t="s" s="6">
+      <c r="B54" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A55" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>29</v>
       </c>
     </row>
-    <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" t="s" s="6">
+    <row r="56" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A56" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="7">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" t="s" s="6">
+      <c r="B56" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A57" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" t="s" s="6">
+    <row r="58" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A58" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" t="s" s="6">
+      <c r="B58" s="6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A59" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="7">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" t="s" s="6">
+      <c r="B59" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A60" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="6">
         <v>32</v>
       </c>
     </row>
-    <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" t="s" s="6">
+    <row r="61" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A61" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" t="s" s="6">
+      <c r="B61" s="6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A62" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="7">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" t="s" s="6">
+      <c r="B62" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A63" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="6">
         <v>34</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" t="s" s="6">
+    <row r="64" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A64" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="7">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" t="s" s="6">
+      <c r="B64" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A65" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="7">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" ht="22.5" customHeight="1">
-      <c r="A66" t="s" s="6">
+      <c r="B65" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A66" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="6">
         <v>36</v>
       </c>
     </row>
-    <row r="67" ht="22.5" customHeight="1">
-      <c r="A67" t="s" s="6">
+    <row r="67" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A67" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="7">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" ht="22.5" customHeight="1">
-      <c r="A68" t="s" s="6">
+      <c r="B67" s="6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A68" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="7">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="69" ht="22.5" customHeight="1">
-      <c r="A69" t="s" s="6">
+      <c r="B68" s="6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A69" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="6">
         <v>38</v>
       </c>
     </row>
-    <row r="70" ht="22.5" customHeight="1">
-      <c r="A70" t="s" s="6">
+    <row r="70" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A70" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="7">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="71" ht="22.5" customHeight="1">
-      <c r="A71" t="s" s="6">
+      <c r="B70" s="6">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A71" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="7">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="72" ht="22.5" customHeight="1">
-      <c r="A72" t="s" s="6">
+      <c r="B71" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A72" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" t="s" s="6">
+    <row r="73" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A73" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="7">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" ht="22.5" customHeight="1">
-      <c r="A74" t="s" s="6">
+      <c r="B73" s="6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A74" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="6">
         <v>41</v>
       </c>
     </row>
-    <row r="75" ht="22.5" customHeight="1">
-      <c r="A75" t="s" s="6">
+    <row r="75" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A75" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="7">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="76" ht="22.5" customHeight="1">
-      <c r="A76" t="s" s="6">
+      <c r="B75" s="6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A76" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="6">
         <v>42</v>
       </c>
     </row>
-    <row r="77" ht="22.5" customHeight="1">
-      <c r="A77" t="s" s="6">
+    <row r="77" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A77" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="7">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="78" ht="22.5" customHeight="1">
-      <c r="A78" t="s" s="6">
+      <c r="B77" s="6">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A78" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="6">
         <v>43</v>
       </c>
     </row>
-    <row r="79" ht="22.5" customHeight="1">
-      <c r="A79" t="s" s="6">
+    <row r="79" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A79" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="7">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" ht="22.5" customHeight="1">
-      <c r="A80" t="s" s="6">
+      <c r="B79" s="6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A80" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="6">
         <v>44</v>
       </c>
     </row>
-    <row r="81" ht="22.5" customHeight="1">
-      <c r="A81" t="s" s="6">
+    <row r="81" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A81" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="6">
         <v>44</v>
       </c>
     </row>
-    <row r="82" ht="22.5" customHeight="1">
-      <c r="A82" t="s" s="6">
+    <row r="82" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A82" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="7">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="83" ht="22.5" customHeight="1">
-      <c r="A83" t="s" s="6">
+      <c r="B82" s="6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A83" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="7">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="84" ht="22.5" customHeight="1">
-      <c r="A84" t="s" s="6">
+      <c r="B83" s="6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A84" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="6">
         <v>46</v>
       </c>
     </row>
-    <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" t="s" s="6">
+    <row r="85" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A85" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="7">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="86" ht="22.5" customHeight="1">
-      <c r="A86" t="s" s="6">
+      <c r="B85" s="6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A86" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="6">
         <v>47</v>
       </c>
     </row>
-    <row r="87" ht="22.5" customHeight="1">
-      <c r="A87" t="s" s="6">
+    <row r="87" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A87" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="7">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="88" ht="22.5" customHeight="1">
-      <c r="A88" t="s" s="6">
+      <c r="B87" s="6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A88" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="6">
         <v>48</v>
       </c>
     </row>
-    <row r="89" ht="22.5" customHeight="1">
-      <c r="A89" t="s" s="6">
+    <row r="89" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A89" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="7">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="90" ht="22.5" customHeight="1">
-      <c r="A90" t="s" s="6">
+      <c r="B89" s="6">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A90" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="6">
         <v>49</v>
       </c>
     </row>
-    <row r="91" ht="22.5" customHeight="1">
-      <c r="A91" t="s" s="6">
+    <row r="91" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A91" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="6">
         <v>49</v>
       </c>
     </row>
-    <row r="92" ht="22.5" customHeight="1">
-      <c r="A92" t="s" s="6">
+    <row r="92" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A92" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="7">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="93" ht="22.5" customHeight="1">
-      <c r="A93" t="s" s="6">
+      <c r="B92" s="6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A93" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="6">
         <v>50</v>
       </c>
     </row>
-    <row r="94" ht="22.5" customHeight="1">
-      <c r="A94" t="s" s="6">
+    <row r="94" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A94" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="95" ht="22.5" customHeight="1">
-      <c r="A95" t="s" s="6">
+      <c r="B94" s="6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A95" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="6">
         <v>51</v>
       </c>
     </row>
-    <row r="96" ht="22.5" customHeight="1">
-      <c r="A96" t="s" s="6">
+    <row r="96" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A96" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B96" s="7">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="97" ht="22.5" customHeight="1">
-      <c r="A97" t="s" s="6">
+      <c r="B96" s="6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A97" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="6">
         <v>52</v>
       </c>
     </row>
-    <row r="98" ht="22.5" customHeight="1">
-      <c r="A98" t="s" s="6">
+    <row r="98" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A98" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B98" s="7">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="99" ht="22.5" customHeight="1">
-      <c r="A99" t="s" s="6">
+      <c r="B98" s="6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A99" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="6">
         <v>53</v>
       </c>
     </row>
-    <row r="100" ht="22.5" customHeight="1">
-      <c r="A100" t="s" s="6">
+    <row r="100" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A100" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B100" s="7">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="101" ht="22.5" customHeight="1">
-      <c r="A101" t="s" s="6">
+      <c r="B100" s="6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A101" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="6">
         <v>54</v>
       </c>
     </row>
-    <row r="102" ht="22.5" customHeight="1">
-      <c r="A102" t="s" s="6">
+    <row r="102" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A102" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="103" ht="22.5" customHeight="1">
-      <c r="A103" t="s" s="6">
+      <c r="B102" s="6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A103" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="6">
         <v>55</v>
       </c>
     </row>
-    <row r="104" ht="22.5" customHeight="1">
-      <c r="A104" t="s" s="6">
+    <row r="104" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A104" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B104" s="7">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="105" ht="22.5" customHeight="1">
-      <c r="A105" t="s" s="6">
+      <c r="B104" s="6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A105" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="6">
         <v>56</v>
       </c>
     </row>
-    <row r="106" ht="22.5" customHeight="1">
-      <c r="A106" t="s" s="6">
+    <row r="106" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A106" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B106" s="7">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="107" ht="22.5" customHeight="1">
-      <c r="A107" t="s" s="6">
+      <c r="B106" s="6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A107" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B107" s="7">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="108" ht="22.5" customHeight="1">
-      <c r="A108" t="s" s="6">
+      <c r="B107" s="6">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A108" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B108" s="7">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="109" ht="22.5" customHeight="1">
-      <c r="A109" t="s" s="6">
+      <c r="B108" s="6">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A109" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="6">
         <v>59</v>
       </c>
     </row>
-    <row r="110" ht="22.5" customHeight="1">
-      <c r="A110" t="s" s="6">
+    <row r="110" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A110" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B110" s="7">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="111" ht="22.5" customHeight="1">
-      <c r="A111" t="s" s="6">
+      <c r="B110" s="6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A111" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="6">
         <v>60</v>
       </c>
     </row>
-    <row r="112" ht="22.5" customHeight="1">
-      <c r="A112" t="s" s="6">
+    <row r="112" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A112" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B112" s="7">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="113" ht="22.5" customHeight="1">
-      <c r="A113" t="s" s="6">
+      <c r="B112" s="6">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A113" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B113" s="7">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="114" ht="22.5" customHeight="1">
-      <c r="A114" t="s" s="6">
+      <c r="B113" s="6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A114" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="6">
         <v>62</v>
       </c>
     </row>
-    <row r="115" ht="22.5" customHeight="1">
-      <c r="A115" t="s" s="6">
+    <row r="115" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A115" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B115" s="7">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="116" ht="22.5" customHeight="1">
-      <c r="A116" t="s" s="6">
+      <c r="B115" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A116" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="6">
         <v>63</v>
       </c>
     </row>
-    <row r="117" ht="22.5" customHeight="1">
-      <c r="A117" t="s" s="6">
+    <row r="117" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A117" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="7">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="118" ht="22.5" customHeight="1">
-      <c r="A118" t="s" s="6">
+      <c r="B117" s="6">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A118" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="6">
         <v>64</v>
       </c>
     </row>
-    <row r="119" ht="22.5" customHeight="1">
-      <c r="A119" t="s" s="6">
+    <row r="119" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A119" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B119" s="7">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="120" ht="22.5" customHeight="1">
-      <c r="A120" t="s" s="6">
+      <c r="B119" s="6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A120" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="6">
         <v>65</v>
       </c>
     </row>
-    <row r="121" ht="22.5" customHeight="1">
-      <c r="A121" t="s" s="6">
+    <row r="121" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A121" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B121" s="7">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="122" ht="22.5" customHeight="1">
-      <c r="A122" t="s" s="6">
+      <c r="B121" s="6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A122" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="6">
         <v>66</v>
       </c>
     </row>
-    <row r="123" ht="22.5" customHeight="1">
-      <c r="A123" t="s" s="6">
+    <row r="123" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A123" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="6">
         <v>66</v>
       </c>
     </row>
-    <row r="124" ht="22.5" customHeight="1">
-      <c r="A124" t="s" s="6">
+    <row r="124" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A124" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B124" s="7">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="125" ht="22.5" customHeight="1">
-      <c r="A125" t="s" s="6">
+      <c r="B124" s="6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A125" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="6">
         <v>67</v>
       </c>
     </row>
-    <row r="126" ht="22.5" customHeight="1">
-      <c r="A126" t="s" s="6">
+    <row r="126" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A126" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B126" s="7">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="127" ht="22.5" customHeight="1">
-      <c r="A127" t="s" s="6">
+      <c r="B126" s="6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A127" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="6">
         <v>68</v>
       </c>
     </row>
-    <row r="128" ht="22.5" customHeight="1">
-      <c r="A128" t="s" s="6">
+    <row r="128" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A128" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="6">
         <v>68</v>
       </c>
     </row>
-    <row r="129" ht="22.5" customHeight="1">
-      <c r="A129" t="s" s="6">
+    <row r="129" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A129" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B129" s="7">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="130" ht="22.5" customHeight="1">
-      <c r="A130" t="s" s="6">
+      <c r="B129" s="6">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A130" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="6">
         <v>69</v>
       </c>
     </row>
-    <row r="131" ht="22.5" customHeight="1">
-      <c r="A131" t="s" s="6">
+    <row r="131" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A131" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B131" s="7">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="132" ht="22.5" customHeight="1">
-      <c r="A132" t="s" s="6">
+      <c r="B131" s="6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A132" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B132" s="7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="133" ht="22.5" customHeight="1">
-      <c r="A133" t="s" s="6">
+      <c r="B132" s="6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A133" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B133" s="7">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="134" ht="22.5" customHeight="1">
-      <c r="A134" t="s" s="6">
+      <c r="B133" s="6">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A134" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="6">
         <v>72</v>
       </c>
     </row>
-    <row r="135" ht="22.5" customHeight="1">
-      <c r="A135" t="s" s="6">
+    <row r="135" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A135" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B135" s="7">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="136" ht="22.5" customHeight="1">
-      <c r="A136" t="s" s="6">
+      <c r="B135" s="6">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A136" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="6">
         <v>73</v>
       </c>
     </row>
-    <row r="137" ht="22.5" customHeight="1">
-      <c r="A137" t="s" s="6">
+    <row r="137" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A137" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B137" s="7">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="138" ht="22.5" customHeight="1">
-      <c r="A138" t="s" s="6">
+      <c r="B137" s="6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A138" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B138" s="7">
+      <c r="B138" s="6">
         <v>74</v>
       </c>
     </row>
-    <row r="139" ht="22.5" customHeight="1">
-      <c r="A139" t="s" s="6">
+    <row r="139" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A139" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="6">
         <v>74</v>
       </c>
     </row>
-    <row r="140" ht="22.5" customHeight="1">
-      <c r="A140" t="s" s="6">
+    <row r="140" spans="1:2" ht="36.450000000000003" customHeight="1">
+      <c r="A140" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="6">
         <v>74</v>
       </c>
     </row>
-    <row r="141" ht="36.5" customHeight="1">
-      <c r="A141" t="s" s="6">
+    <row r="141" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A141" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B141" s="7">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="142" ht="22.5" customHeight="1">
-      <c r="A142" t="s" s="6">
+      <c r="B141" s="6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A142" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="6">
         <v>75</v>
       </c>
     </row>
-    <row r="143" ht="22.5" customHeight="1">
-      <c r="A143" t="s" s="6">
+    <row r="143" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A143" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B143" s="7">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="144" ht="22.5" customHeight="1">
-      <c r="A144" t="s" s="6">
+      <c r="B143" s="6">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A144" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="6">
         <v>76</v>
       </c>
     </row>
-    <row r="145" ht="22.5" customHeight="1">
-      <c r="A145" t="s" s="6">
+    <row r="145" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A145" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B145" s="7">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="146" ht="22.5" customHeight="1">
-      <c r="A146" t="s" s="6">
+      <c r="B145" s="6">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A146" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="6">
         <v>77</v>
       </c>
     </row>
-    <row r="147" ht="22.5" customHeight="1">
-      <c r="A147" t="s" s="6">
+    <row r="147" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A147" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B147" s="7">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="148" ht="22.5" customHeight="1">
-      <c r="A148" t="s" s="6">
+      <c r="B147" s="6">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A148" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="6">
         <v>78</v>
       </c>
     </row>
-    <row r="149" ht="22.5" customHeight="1">
-      <c r="A149" t="s" s="6">
+    <row r="149" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A149" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B149" s="7">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="150" ht="22.5" customHeight="1">
-      <c r="A150" t="s" s="6">
+      <c r="B149" s="6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A150" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B150" s="7">
+      <c r="B150" s="6">
         <v>79</v>
       </c>
     </row>
-    <row r="151" ht="22.5" customHeight="1">
-      <c r="A151" t="s" s="6">
+    <row r="151" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A151" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B151" s="7">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="152" ht="22.5" customHeight="1">
-      <c r="A152" t="s" s="6">
+      <c r="B151" s="6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A152" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B152" s="7">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="153" ht="22.5" customHeight="1">
-      <c r="A153" t="s" s="6">
+      <c r="B152" s="6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A153" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B153" s="7">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="154" ht="22.5" customHeight="1">
-      <c r="A154" t="s" s="6">
+      <c r="B153" s="6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A154" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B154" s="6">
         <v>82</v>
       </c>
     </row>
-    <row r="155" ht="22.5" customHeight="1">
-      <c r="A155" t="s" s="6">
+    <row r="155" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A155" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B155" s="7">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="156" ht="22.5" customHeight="1">
-      <c r="A156" t="s" s="6">
+      <c r="B155" s="6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A156" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B156" s="7">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="157" ht="22.5" customHeight="1">
-      <c r="A157" t="s" s="6">
+      <c r="B156" s="6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A157" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B157" s="7">
+      <c r="B157" s="6">
         <v>84</v>
       </c>
     </row>
-    <row r="158" ht="22.5" customHeight="1">
-      <c r="A158" t="s" s="6">
+    <row r="158" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A158" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B158" s="7">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="159" ht="22.5" customHeight="1">
-      <c r="A159" t="s" s="6">
+      <c r="B158" s="6">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A159" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B159" s="7">
+      <c r="B159" s="6">
         <v>85</v>
       </c>
     </row>
-    <row r="160" ht="22.5" customHeight="1">
-      <c r="A160" t="s" s="6">
+    <row r="160" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A160" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B160" s="7">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="161" ht="22.5" customHeight="1">
-      <c r="A161" t="s" s="6">
+      <c r="B160" s="6">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A161" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B161" s="7">
+      <c r="B161" s="6">
         <v>86</v>
       </c>
     </row>
-    <row r="162" ht="22.5" customHeight="1">
-      <c r="A162" t="s" s="6">
+    <row r="162" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A162" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B162" s="7">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="163" ht="22.5" customHeight="1">
-      <c r="A163" t="s" s="6">
+      <c r="B162" s="6">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A163" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B163" s="7">
+      <c r="B163" s="6">
         <v>87</v>
       </c>
     </row>
-    <row r="164" ht="22.5" customHeight="1">
-      <c r="A164" t="s" s="6">
+    <row r="164" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A164" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B164" s="7">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="165" ht="22.5" customHeight="1">
-      <c r="A165" t="s" s="6">
+      <c r="B164" s="6">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A165" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B165" s="7">
+      <c r="B165" s="6">
         <v>88</v>
       </c>
     </row>
-    <row r="166" ht="22.5" customHeight="1">
-      <c r="A166" t="s" s="6">
+    <row r="166" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A166" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B166" s="7">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="167" ht="22.5" customHeight="1">
-      <c r="A167" t="s" s="6">
+      <c r="B166" s="6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A167" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B167" s="7">
+      <c r="B167" s="6">
         <v>89</v>
       </c>
     </row>
-    <row r="168" ht="22.5" customHeight="1">
-      <c r="A168" t="s" s="6">
+    <row r="168" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A168" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B168" s="7">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="169" ht="22.5" customHeight="1">
-      <c r="A169" t="s" s="6">
+      <c r="B168" s="6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A169" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B169" s="7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="170" ht="22.5" customHeight="1">
-      <c r="A170" t="s" s="6">
+      <c r="B169" s="6">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A170" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B170" s="7">
+      <c r="B170" s="6">
         <v>91</v>
       </c>
     </row>
-    <row r="171" ht="22.5" customHeight="1">
-      <c r="A171" t="s" s="6">
+    <row r="171" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A171" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B171" s="7">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="172" ht="22.5" customHeight="1">
-      <c r="A172" t="s" s="6">
+      <c r="B171" s="6">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A172" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B172" s="7">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="173" ht="22.5" customHeight="1">
-      <c r="A173" t="s" s="6">
+      <c r="B172" s="6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A173" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B173" s="7">
+      <c r="B173" s="6">
         <v>93</v>
       </c>
     </row>
-    <row r="174" ht="22.5" customHeight="1">
-      <c r="A174" t="s" s="6">
+    <row r="174" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A174" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B174" s="7">
+      <c r="B174" s="6">
         <v>93</v>
       </c>
     </row>
-    <row r="175" ht="22.5" customHeight="1">
-      <c r="A175" t="s" s="6">
+    <row r="175" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A175" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B175" s="7">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="176" ht="22.5" customHeight="1">
-      <c r="A176" t="s" s="6">
+      <c r="B175" s="6">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A176" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B176" s="7">
+      <c r="B176" s="6">
         <v>94</v>
       </c>
     </row>
-    <row r="177" ht="22.5" customHeight="1">
-      <c r="A177" t="s" s="6">
+    <row r="177" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A177" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B177" s="7">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="178" ht="22.5" customHeight="1">
-      <c r="A178" t="s" s="6">
+      <c r="B177" s="6">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A178" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B178" s="7">
+      <c r="B178" s="6">
         <v>95</v>
       </c>
     </row>
-    <row r="179" ht="22.5" customHeight="1">
-      <c r="A179" t="s" s="6">
+    <row r="179" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A179" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B179" s="7">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="180" ht="22.5" customHeight="1">
-      <c r="A180" t="s" s="6">
+      <c r="B179" s="6">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A180" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B180" s="7">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="181" ht="22.5" customHeight="1">
-      <c r="A181" t="s" s="6">
+      <c r="B180" s="6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A181" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B181" s="7">
+      <c r="B181" s="6">
         <v>97</v>
       </c>
     </row>
-    <row r="182" ht="22.5" customHeight="1">
-      <c r="A182" t="s" s="6">
+    <row r="182" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A182" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B182" s="7">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="183" ht="22.5" customHeight="1">
-      <c r="A183" t="s" s="6">
+      <c r="B182" s="6">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A183" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B183" s="7">
+      <c r="B183" s="6">
         <v>98</v>
       </c>
     </row>
-    <row r="184" ht="22.5" customHeight="1">
-      <c r="A184" t="s" s="6">
+    <row r="184" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A184" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B184" s="7">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="185" ht="22.5" customHeight="1">
-      <c r="A185" t="s" s="6">
+      <c r="B184" s="6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A185" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B185" s="7">
+      <c r="B185" s="6">
         <v>99</v>
       </c>
     </row>
-    <row r="186" ht="22.5" customHeight="1">
-      <c r="A186" t="s" s="6">
+    <row r="186" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A186" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B186" s="7">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="187" ht="22.5" customHeight="1">
-      <c r="A187" t="s" s="6">
+      <c r="B186" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A187" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="B187" s="7">
+      <c r="B187" s="6">
         <v>100</v>
       </c>
     </row>
-    <row r="188" ht="22.5" customHeight="1">
-      <c r="A188" t="s" s="6">
+    <row r="188" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A188" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B188" s="7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="189" ht="22.5" customHeight="1">
-      <c r="A189" t="s" s="6">
+      <c r="B188" s="6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A189" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B189" s="7">
+      <c r="B189" s="6">
         <v>101</v>
       </c>
     </row>
-    <row r="190" ht="22.5" customHeight="1">
-      <c r="A190" t="s" s="6">
+    <row r="190" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A190" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B190" s="7">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="191" ht="22.5" customHeight="1">
-      <c r="A191" t="s" s="6">
+      <c r="B190" s="6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A191" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="B191" s="7">
+      <c r="B191" s="6">
         <v>102</v>
       </c>
     </row>
-    <row r="192" ht="22.5" customHeight="1">
-      <c r="A192" t="s" s="6">
+    <row r="192" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A192" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B192" s="7">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="193" ht="22.5" customHeight="1">
-      <c r="A193" t="s" s="6">
+      <c r="B192" s="6">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A193" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B193" s="7">
+      <c r="B193" s="6">
         <v>103</v>
       </c>
     </row>
-    <row r="194" ht="22.5" customHeight="1">
-      <c r="A194" t="s" s="6">
+    <row r="194" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A194" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B194" s="7">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="195" ht="22.5" customHeight="1">
-      <c r="A195" t="s" s="6">
+      <c r="B194" s="6">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A195" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B195" s="7">
+      <c r="B195" s="6">
         <v>104</v>
       </c>
     </row>
-    <row r="196" ht="22.5" customHeight="1">
-      <c r="A196" t="s" s="6">
+    <row r="196" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A196" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B196" s="7">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="197" ht="22.5" customHeight="1">
-      <c r="A197" t="s" s="6">
+      <c r="B196" s="6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A197" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B197" s="7">
+      <c r="B197" s="6">
         <v>105</v>
       </c>
     </row>
-    <row r="198" ht="22.5" customHeight="1">
-      <c r="A198" t="s" s="6">
+    <row r="198" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A198" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B198" s="7">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="199" ht="22.5" customHeight="1">
-      <c r="A199" t="s" s="6">
+      <c r="B198" s="6">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A199" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B199" s="7">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="200" ht="22.5" customHeight="1">
-      <c r="A200" t="s" s="6">
+      <c r="B199" s="6">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A200" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B200" s="7">
+      <c r="B200" s="6">
         <v>107</v>
       </c>
     </row>
-    <row r="201" ht="22.5" customHeight="1">
-      <c r="A201" t="s" s="6">
+    <row r="201" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A201" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B201" s="7">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="202" ht="22.5" customHeight="1">
-      <c r="A202" t="s" s="6">
+      <c r="B201" s="6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A202" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B202" s="7">
+      <c r="B202" s="6">
         <v>108</v>
       </c>
     </row>
-    <row r="203" ht="22.5" customHeight="1">
-      <c r="A203" t="s" s="6">
+    <row r="203" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A203" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B203" s="7">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="204" ht="22.5" customHeight="1">
-      <c r="A204" t="s" s="6">
+      <c r="B203" s="6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A204" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B204" s="7">
+      <c r="B204" s="6">
         <v>109</v>
       </c>
     </row>
-    <row r="205" ht="22.5" customHeight="1">
-      <c r="A205" t="s" s="6">
+    <row r="205" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A205" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B205" s="7">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="206" ht="22.5" customHeight="1">
-      <c r="A206" t="s" s="6">
+      <c r="B205" s="6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A206" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="B206" s="7">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="207" ht="22.5" customHeight="1">
-      <c r="A207" t="s" s="6">
+      <c r="B206" s="6">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A207" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B207" s="7">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="208" ht="22.5" customHeight="1">
-      <c r="A208" t="s" s="6">
+      <c r="B207" s="6">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A208" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B208" s="7">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="209" ht="22.5" customHeight="1">
-      <c r="A209" t="s" s="6">
+      <c r="B208" s="6">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A209" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B209" s="7">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="210" ht="22.5" customHeight="1">
-      <c r="A210" t="s" s="6">
+      <c r="B209" s="6">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A210" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B210" s="7">
+      <c r="B210" s="6">
         <v>115</v>
       </c>
     </row>
-    <row r="211" ht="22.5" customHeight="1">
-      <c r="A211" t="s" s="6">
+    <row r="211" spans="1:2" ht="22.8" customHeight="1">
+      <c r="A211" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B211" s="7">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="212" ht="22.75" customHeight="1">
-      <c r="A212" t="s" s="14">
-        <v>210</v>
-      </c>
-      <c r="B212" s="15">
+      <c r="B211" s="14">
         <v>116</v>
       </c>
     </row>
-    <row r="213" ht="20.75" customHeight="1">
-      <c r="A213" s="16"/>
-      <c r="B213" s="16"/>
+    <row r="212" spans="1:2" ht="20.7" customHeight="1">
+      <c r="A212" s="15"/>
+      <c r="B212" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
+  <pageSetup scale="72" orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/prisma/guest.xlsx
+++ b/prisma/guest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karla\Documents\GitHub\wedding_backend\prisma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E36AF1-80C3-4469-A038-A2970FF893E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116A24AC-1E95-4A26-81E2-D45801DAD229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
   <si>
     <t>Martin Pocasangre</t>
   </si>
@@ -656,6 +656,63 @@
   </si>
   <si>
     <t>Grupo</t>
+  </si>
+  <si>
+    <t>Sergio Calderón</t>
+  </si>
+  <si>
+    <t>Monica de Calderón</t>
+  </si>
+  <si>
+    <t>Alexa Calderón</t>
+  </si>
+  <si>
+    <t>Gerardo Calderón</t>
+  </si>
+  <si>
+    <t>Karen de Calderón</t>
+  </si>
+  <si>
+    <t>Sofia Nolasco</t>
+  </si>
+  <si>
+    <t>Camila Nolasco</t>
+  </si>
+  <si>
+    <t>Alessandra Sol</t>
+  </si>
+  <si>
+    <t>Raúl Lara</t>
+  </si>
+  <si>
+    <t>Claudia Cárcamo de Lara</t>
+  </si>
+  <si>
+    <t>Juan Carlos Bruno</t>
+  </si>
+  <si>
+    <t>Brenda Cárcamo de Bruno</t>
+  </si>
+  <si>
+    <t>José Ricardo Flores</t>
+  </si>
+  <si>
+    <t>Lorena Cárcamo de Flores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rocío Liliana Cárcamo </t>
+  </si>
+  <si>
+    <t>Rosa Yanira Castrillo</t>
+  </si>
+  <si>
+    <t>Violeta Patricia Cárcamo</t>
+  </si>
+  <si>
+    <t>Carlos Eduardo Aguilar</t>
+  </si>
+  <si>
+    <t>Tania de Aguilar</t>
   </si>
 </sst>
 </file>
@@ -685,9 +742,10 @@
       <name val="Avenir Next Regular"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Proxima Nova Medium"/>
+      <name val="Proxima Nova"/>
     </font>
   </fonts>
   <fills count="5">
@@ -716,7 +774,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -769,13 +827,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -821,7 +907,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1951,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B212"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.33203125" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="22.6640625" style="1" customWidth="1"/>
@@ -3623,7 +3727,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="22.5" customHeight="1">
+    <row r="209" spans="1:4" ht="22.5" customHeight="1">
       <c r="A209" s="5" t="s">
         <v>207</v>
       </c>
@@ -3631,7 +3735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="22.5" customHeight="1">
+    <row r="210" spans="1:4" ht="22.5" customHeight="1">
       <c r="A210" s="5" t="s">
         <v>208</v>
       </c>
@@ -3639,7 +3743,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="22.8" customHeight="1">
+    <row r="211" spans="1:4" ht="22.8" customHeight="1">
       <c r="A211" s="13" t="s">
         <v>209</v>
       </c>
@@ -3647,13 +3751,178 @@
         <v>116</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="20.7" customHeight="1">
-      <c r="A212" s="15"/>
-      <c r="B212" s="15"/>
+    <row r="212" spans="1:4" ht="20.7" customHeight="1">
+      <c r="A212" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" s="16">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="18" customHeight="1">
+      <c r="A213" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" s="16">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="18" customHeight="1">
+      <c r="A214" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" s="16">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="18" customHeight="1">
+      <c r="A215" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" s="16">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="18" customHeight="1">
+      <c r="A216" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" s="16">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="18" customHeight="1">
+      <c r="A217" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B217" s="16">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="18" customHeight="1">
+      <c r="A218" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" s="16">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="18" customHeight="1">
+      <c r="A219" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" s="18">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="18" customHeight="1">
+      <c r="A220" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" s="19">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="18" customHeight="1">
+      <c r="A221" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" s="19">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="18" customHeight="1">
+      <c r="A222" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" s="19">
+        <v>121</v>
+      </c>
+      <c r="D222" s="20"/>
+    </row>
+    <row r="223" spans="1:4" ht="18" customHeight="1">
+      <c r="A223" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" s="19">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="18" customHeight="1">
+      <c r="A224" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" s="19">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="18" customHeight="1">
+      <c r="A225" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" s="19">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="18" customHeight="1">
+      <c r="A226" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B226" s="19">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="18" customHeight="1">
+      <c r="A227" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B227" s="19">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="18" customHeight="1">
+      <c r="A228" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B228" s="19">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="18" customHeight="1">
+      <c r="A229" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" s="19">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="18" customHeight="1">
+      <c r="A230" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B230" s="19">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="18" customHeight="1">
+      <c r="A231" s="21"/>
+      <c r="B231" s="21"/>
+    </row>
+    <row r="232" spans="1:2" ht="18" customHeight="1">
+      <c r="A232" s="21"/>
+      <c r="B232" s="21"/>
+    </row>
+    <row r="233" spans="1:2" ht="18" customHeight="1">
+      <c r="A233" s="21"/>
+      <c r="B233" s="21"/>
+    </row>
+    <row r="234" spans="1:2" ht="18" customHeight="1">
+      <c r="A234" s="21"/>
+      <c r="B234" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.27777800000000002" footer="0.27777800000000002"/>
-  <pageSetup scale="72" orientation="portrait"/>
+  <pageSetup scale="72" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
